--- a/output/graficos_nacionales/plot_nacional_regiones_i_ingr_a_2023.xlsx
+++ b/output/graficos_nacionales/plot_nacional_regiones_i_ingr_a_2023.xlsx
@@ -78,7 +78,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-07 12:16</t>
+    <t xml:space="preserve">2026-09-09 21:00</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_regiones_i_ingr_a_2023.xlsx
+++ b/output/graficos_nacionales/plot_nacional_regiones_i_ingr_a_2023.xlsx
@@ -78,7 +78,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 21:00</t>
+    <t xml:space="preserve">2026-09-17 13:48</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_regiones_i_ingr_a_2023.xlsx
+++ b/output/graficos_nacionales/plot_nacional_regiones_i_ingr_a_2023.xlsx
@@ -78,7 +78,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 13:48</t>
+    <t xml:space="preserve">2026-10-05 18:55</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -490,7 +490,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>1419730.62</v>
+        <v>1419730.63</v>
       </c>
     </row>
     <row r="3">
@@ -498,7 +498,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>1099959.12</v>
+        <v>1099959.13</v>
       </c>
     </row>
     <row r="4">
@@ -514,7 +514,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>1166918.62</v>
+        <v>1166918.63</v>
       </c>
     </row>
     <row r="6">
@@ -554,7 +554,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>1017403.62</v>
+        <v>1017403.63</v>
       </c>
     </row>
     <row r="11">
@@ -562,7 +562,7 @@
         <v>11</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>1212855.12</v>
+        <v>1212855.13</v>
       </c>
     </row>
     <row r="12">
@@ -586,7 +586,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>1030063.12</v>
+        <v>1030063.13</v>
       </c>
     </row>
     <row r="15">
